--- a/outputs/374-31.xlsx
+++ b/outputs/374-31.xlsx
@@ -20,21 +20,46 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t xml:space="preserve">Sub DelBlankAboveCode()</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Dim r As Long, i As Long</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    r = Columns(1).Find("Code").Row</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    For i = r - 1 To 1 Step -1: If Cells(i, 1) = "" Then Rows(i).Delete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Next: End Sub</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t xml:space="preserve">Sub DeleteBlankRowsAboveCode()
+    Dim codeRow As Long
+    Dim i As Long
+    ' Find the row containing "Code" in column A
+    codeRow = 0
+    For i = 1 To Cells(Rows.Count, 1).End(xlUp).Row
+        If Cells(i, 1).Value = "Code" Then
+            codeRow = i
+            Exit For
+        End If
+    Next i
+    ' Delete blank rows above the Code row
+    If codeRow &gt; 1 Then
+        For i = codeRow - 1 To 1 Step -1
+            If Cells(i, 1).Value = "" Then
+                Rows(i).Delete
+            End If
+        Next i
+    End If
+End Sub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Address2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BR1 Southern SalesLedgerOutstandingTransactions ALL AUG21.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Address1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dave Marks</t>
   </si>
 </sst>
 </file>
@@ -110,8 +135,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -304,41 +337,46 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" customFormat="false" ht="914.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="2" t="n">
+        <v>44449.4781018519</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="n">
+        <v>98715</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/outputs/374-31.xlsx
+++ b/outputs/374-31.xlsx
@@ -22,25 +22,22 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
-    <t xml:space="preserve">Sub DeleteBlankRowsAboveCode()
-    Dim codeRow As Long
+    <t xml:space="preserve">Sub DeleteBlankRows()
+    Dim ws As Worksheet
+    Set ws = ThisWorkbook.Sheets("Sheet1")
+    Dim lastRow As Long
+    lastRow = ws.Cells(ws.Rows.Count, 1).End(xlUp).Row
     Dim i As Long
-    ' Find the row containing "Code" in column A
-    codeRow = 0
-    For i = 1 To Cells(Rows.Count, 1).End(xlUp).Row
-        If Cells(i, 1).Value = "Code" Then
-            codeRow = i
-            Exit For
+    For i = lastRow To 1 Step -1
+        If ws.Cells(i, 1).Value = "Code" Then
+            Dim j As Long
+            For j = i - 1 To 1 Step -1
+                If ws.Cells(j, 1).Value = "" Then
+                    ws.Rows(j).Delete
+                End If
+            Next j
         End If
     Next i
-    ' Delete blank rows above the Code row
-    If codeRow &gt; 1 Then
-        For i = codeRow - 1 To 1 Step -1
-            If Cells(i, 1).Value = "" Then
-                Rows(i).Delete
-            End If
-        Next i
-    End If
 End Sub</t>
   </si>
   <si>
@@ -340,7 +337,7 @@
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="914.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="793.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
